--- a/AAII_Financials/Yearly/EVH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EVH_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>EVH</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1963900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1352000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>908000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>924600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>687100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>627100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>435000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>254200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>96900</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>25700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8300</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1503400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1035400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>657600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>696600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>513000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>327800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>269400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>155200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>57400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>72400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>460500</v>
+      </c>
+      <c r="E10" s="3">
         <v>316600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>250400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>228100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>174100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>299200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>165600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>99000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-72400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-4300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-2900</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,93 +961,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>96900</v>
+      </c>
+      <c r="E14" s="3">
         <v>10200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-24600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>267000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>199800</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>160600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-414100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-46200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>123400</v>
+      </c>
+      <c r="E15" s="3">
         <v>67200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>60000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>60800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>60400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>44500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>1200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>700</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2056100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1358600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>925800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1239400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>996000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>674500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>507800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>491600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-274300</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
       <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
         <v>600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-92200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-17800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-314800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-308900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-47500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-72800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-237400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>371200</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
       <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
         <v>25100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19600</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,116 +1179,123 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-40000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>13400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>12600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-27900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-25200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E21" s="3">
         <v>20700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>55700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-240700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-240000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-40400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-220300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>350500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-25200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-18900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E22" s="3">
         <v>15600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>29100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3600</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1272,93 +1311,102 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-202400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-62100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-29800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-330500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-330000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-54200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-76400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-237500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>343300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19600</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-89400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-43400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-22800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-6600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-10800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>23500</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-113000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-30300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-328200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-307200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-54500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-69800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-226800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>319800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19300</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-30300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-328200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-303600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-53000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-60700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-159700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>330300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19300</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,32 +1581,35 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-7300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-2500</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>1600</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>300</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1563,12 +1623,15 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E32" s="3">
         <v>40000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-13400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-12600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>27900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>25200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-37600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-330600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-302000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-52700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-60700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-159700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>330300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-37600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-330600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-302000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-52700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-60700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-159700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>330300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,50 +1987,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>192800</v>
+      </c>
+      <c r="E41" s="3">
         <v>188200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>266300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>319000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>101000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>228300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>238400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>134600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>145700</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>67900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1955,81 +2044,87 @@
       <c r="E42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G42" s="3">
         <v>3900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1800</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>44300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9400</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>446700</v>
+      </c>
+      <c r="E43" s="3">
         <v>254700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>130600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>250400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>77400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>82300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>68900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>40600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2069,219 +2164,237 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E45" s="3">
         <v>35200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>127100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>104600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>48600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>177300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>70800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>45400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>683700</v>
+      </c>
+      <c r="E46" s="3">
         <v>478100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>524000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>547600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>228800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>488000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>378200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>265000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>184500</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3">
         <v>80300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7800</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E47" s="3">
         <v>4500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>180400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>17200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>37200</v>
-      </c>
-      <c r="M47" s="3">
-        <v>2400</v>
       </c>
       <c r="N47" s="3">
         <v>2400</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>90200</v>
+      </c>
+      <c r="E48" s="3">
         <v>136900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>131600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>144000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>157300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>50900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1868600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1165600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>706100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>614000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>880500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1103200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>869400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>885500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>772100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E52" s="3">
         <v>32300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>52400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>59500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>51000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1600</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>3500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2680300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1817300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1419500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1371700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1498000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1722300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1312700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1199800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1015500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>102000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16300</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,65 +2655,69 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E57" s="3">
         <v>57200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>96100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>37500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>146800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>42900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16700</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>26600</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2600,8 +2733,8 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2609,120 +2742,129 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E59" s="3">
         <v>376300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>349400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>344800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>155300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>122600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>89800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>88000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>42800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8800</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>674200</v>
+      </c>
+      <c r="E60" s="3">
         <v>433400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>445500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>403300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>192800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>269400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>132700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>131900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>59500</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3">
         <v>29300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>597000</v>
+      </c>
+      <c r="E61" s="3">
         <v>413000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>215700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>263300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>293700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>221000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>121400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>120300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2735,51 +2877,57 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>162900</v>
+      </c>
+      <c r="E62" s="3">
         <v>111400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>64700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>85500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>82500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>42500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>35500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1434200</v>
+      </c>
+      <c r="E66" s="3">
         <v>957900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>725800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>752100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>575700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>578500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>301800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>497300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>366200</v>
       </c>
-      <c r="L66" s="3">
-        <v>0</v>
-      </c>
       <c r="M66" s="3">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3">
         <v>32700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,14 +3211,17 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>178400</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -3078,20 +3245,23 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>40900</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>69300</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-719200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-606200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-626800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-589200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-252000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>50000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>86000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>146600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>306700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-25800</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
       <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
         <v>-20600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1067700</v>
+      </c>
+      <c r="E76" s="3">
         <v>859400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>693600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>619600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>922400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1143800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1010900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>702500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>649300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-3700</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
       <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
         <v>5200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-37600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-330600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-302000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-52700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-60700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-159700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>330300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>123400</v>
+      </c>
+      <c r="E83" s="3">
         <v>67200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>60000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>61500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>60900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>44500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>32400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7200</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>1200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>142600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-42600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-20700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-35500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-18500</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-13600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-47500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-35500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-39600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6500</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-10400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-415500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-259100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>261100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-181600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-160400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-96700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-43700</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-25900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3800</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,71 +4398,77 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>281300</v>
+      </c>
+      <c r="E100" s="3">
         <v>131500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-29500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-35500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>274000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>165600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>150200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>214200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>34300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4500</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -4237,52 +4485,58 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-139800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>233100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-259800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>93000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>125300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>18000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>152000</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/EVH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EVH_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>EVH</t>
   </si>
@@ -787,7 +787,7 @@
         <v>513000</v>
       </c>
       <c r="I9" s="3">
-        <v>327800</v>
+        <v>398700</v>
       </c>
       <c r="J9" s="3">
         <v>269400</v>
@@ -832,7 +832,7 @@
         <v>174100</v>
       </c>
       <c r="I10" s="3">
-        <v>299200</v>
+        <v>228300</v>
       </c>
       <c r="J10" s="3">
         <v>165600</v>
@@ -880,26 +880,26 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>26500</v>
+      </c>
+      <c r="G12" s="3">
+        <v>24300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>38500</v>
+      </c>
+      <c r="I12" s="3">
+        <v>30600</v>
+      </c>
+      <c r="J12" s="3">
+        <v>22100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>96900</v>
+        <v>123000</v>
       </c>
       <c r="E14" s="3">
-        <v>10200</v>
+        <v>11600</v>
       </c>
       <c r="F14" s="3">
-        <v>-24600</v>
+        <v>400</v>
       </c>
       <c r="G14" s="3">
-        <v>267000</v>
+        <v>284000</v>
       </c>
       <c r="H14" s="3">
-        <v>199800</v>
+        <v>214300</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="K14" s="3">
         <v>160600</v>
@@ -1028,7 +1028,7 @@
         <v>60800</v>
       </c>
       <c r="H15" s="3">
-        <v>60400</v>
+        <v>60300</v>
       </c>
       <c r="I15" s="3">
         <v>44500</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2056100</v>
+        <v>1933100</v>
       </c>
       <c r="E17" s="3">
-        <v>1358600</v>
+        <v>1347000</v>
       </c>
       <c r="F17" s="3">
-        <v>925800</v>
+        <v>925400</v>
       </c>
       <c r="G17" s="3">
-        <v>1239400</v>
+        <v>955500</v>
       </c>
       <c r="H17" s="3">
-        <v>996000</v>
+        <v>781700</v>
       </c>
       <c r="I17" s="3">
-        <v>674500</v>
+        <v>674200</v>
       </c>
       <c r="J17" s="3">
-        <v>507800</v>
+        <v>496900</v>
       </c>
       <c r="K17" s="3">
         <v>491600</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-92200</v>
+        <v>30800</v>
       </c>
       <c r="E18" s="3">
-        <v>-6600</v>
+        <v>5000</v>
       </c>
       <c r="F18" s="3">
-        <v>-17800</v>
+        <v>-17400</v>
       </c>
       <c r="G18" s="3">
-        <v>-314800</v>
+        <v>-30800</v>
       </c>
       <c r="H18" s="3">
-        <v>-308900</v>
+        <v>-94600</v>
       </c>
       <c r="I18" s="3">
-        <v>-47500</v>
+        <v>-47200</v>
       </c>
       <c r="J18" s="3">
-        <v>-72800</v>
+        <v>-61900</v>
       </c>
       <c r="K18" s="3">
         <v>-237400</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-56000</v>
+        <v>61200</v>
       </c>
       <c r="E20" s="3">
-        <v>-40000</v>
+        <v>41300</v>
       </c>
       <c r="F20" s="3">
-        <v>13400</v>
+        <v>-13000</v>
       </c>
       <c r="G20" s="3">
-        <v>12600</v>
+        <v>-9900</v>
       </c>
       <c r="H20" s="3">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="I20" s="3">
-        <v>-1200</v>
+        <v>4600</v>
       </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-24800</v>
+        <v>93000</v>
       </c>
       <c r="E21" s="3">
-        <v>20700</v>
+        <v>30900</v>
       </c>
       <c r="F21" s="3">
         <v>55700</v>
       </c>
       <c r="G21" s="3">
-        <v>-240700</v>
+        <v>39900</v>
       </c>
       <c r="H21" s="3">
-        <v>-240000</v>
+        <v>-44200</v>
       </c>
       <c r="I21" s="3">
-        <v>-4200</v>
+        <v>-7300</v>
       </c>
       <c r="J21" s="3">
-        <v>-40400</v>
+        <v>-31200</v>
       </c>
       <c r="K21" s="3">
         <v>-220300</v>
@@ -1288,7 +1288,7 @@
         <v>28300</v>
       </c>
       <c r="H22" s="3">
-        <v>29100</v>
+        <v>14600</v>
       </c>
       <c r="I22" s="3">
         <v>5500</v>
@@ -1381,7 +1381,7 @@
         <v>-22800</v>
       </c>
       <c r="I24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>-6600</v>
@@ -1471,7 +1471,7 @@
         <v>-307200</v>
       </c>
       <c r="I26" s="3">
-        <v>-54500</v>
+        <v>-54200</v>
       </c>
       <c r="J26" s="3">
         <v>-69800</v>
@@ -1504,19 +1504,19 @@
         <v>-142300</v>
       </c>
       <c r="E27" s="3">
-        <v>-18700</v>
+        <v>-19200</v>
       </c>
       <c r="F27" s="3">
-        <v>-30300</v>
+        <v>-37600</v>
       </c>
       <c r="G27" s="3">
-        <v>-328200</v>
+        <v>-334300</v>
       </c>
       <c r="H27" s="3">
-        <v>-303600</v>
+        <v>-302000</v>
       </c>
       <c r="I27" s="3">
-        <v>-53000</v>
+        <v>-52700</v>
       </c>
       <c r="J27" s="3">
         <v>-60700</v>
@@ -1600,13 +1600,13 @@
         <v>-7300</v>
       </c>
       <c r="G29" s="3">
-        <v>-2500</v>
+        <v>-6100</v>
       </c>
       <c r="H29" s="3">
         <v>1600</v>
       </c>
       <c r="I29" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>56000</v>
+        <v>-61200</v>
       </c>
       <c r="E32" s="3">
-        <v>40000</v>
+        <v>-41300</v>
       </c>
       <c r="F32" s="3">
-        <v>-13400</v>
+        <v>13000</v>
       </c>
       <c r="G32" s="3">
-        <v>-12600</v>
+        <v>9900</v>
       </c>
       <c r="H32" s="3">
-        <v>-8000</v>
+        <v>-10000</v>
       </c>
       <c r="I32" s="3">
-        <v>1200</v>
+        <v>-4600</v>
       </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>-1600</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
@@ -1771,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-142300</v>
+        <v>-113000</v>
       </c>
       <c r="E33" s="3">
         <v>-19200</v>
@@ -1780,7 +1780,7 @@
         <v>-37600</v>
       </c>
       <c r="G33" s="3">
-        <v>-330600</v>
+        <v>-334200</v>
       </c>
       <c r="H33" s="3">
         <v>-302000</v>
@@ -1861,7 +1861,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-142300</v>
+        <v>-113000</v>
       </c>
       <c r="E35" s="3">
         <v>-19200</v>
@@ -1870,7 +1870,7 @@
         <v>-37600</v>
       </c>
       <c r="G35" s="3">
-        <v>-330600</v>
+        <v>-334200</v>
       </c>
       <c r="H35" s="3">
         <v>-302000</v>
@@ -2038,23 +2038,23 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>1800</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>130600</v>
       </c>
       <c r="G43" s="3">
-        <v>250400</v>
+        <v>124400</v>
       </c>
       <c r="H43" s="3">
         <v>77400</v>
@@ -2128,26 +2128,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2173,26 +2173,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>44100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>35200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>127100</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
-        <v>104600</v>
+        <v>33900</v>
       </c>
       <c r="H45" s="3">
-        <v>48600</v>
+        <v>700</v>
       </c>
       <c r="I45" s="3">
-        <v>177300</v>
+        <v>200</v>
       </c>
       <c r="J45" s="3">
-        <v>70800</v>
+        <v>8200</v>
       </c>
       <c r="K45" s="3">
         <v>45400</v>
@@ -2273,13 +2273,13 @@
         <v>5500</v>
       </c>
       <c r="G47" s="3">
-        <v>17400</v>
+        <v>6500</v>
       </c>
       <c r="H47" s="3">
-        <v>180400</v>
+        <v>139400</v>
       </c>
       <c r="I47" s="3">
-        <v>17200</v>
+        <v>16300</v>
       </c>
       <c r="J47" s="3">
         <v>1500</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>90200</v>
+        <v>19300</v>
       </c>
       <c r="E48" s="3">
-        <v>136900</v>
+        <v>63200</v>
       </c>
       <c r="F48" s="3">
-        <v>131600</v>
+        <v>60400</v>
       </c>
       <c r="G48" s="3">
-        <v>144000</v>
+        <v>68700</v>
       </c>
       <c r="H48" s="3">
-        <v>157300</v>
+        <v>82400</v>
       </c>
       <c r="I48" s="3">
-        <v>73600</v>
+        <v>10800</v>
       </c>
       <c r="J48" s="3">
-        <v>50900</v>
+        <v>8800</v>
       </c>
       <c r="K48" s="3">
         <v>31200</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1868600</v>
+        <v>1939500</v>
       </c>
       <c r="E49" s="3">
-        <v>1165600</v>
+        <v>1239300</v>
       </c>
       <c r="F49" s="3">
-        <v>706100</v>
+        <v>777300</v>
       </c>
       <c r="G49" s="3">
-        <v>614000</v>
+        <v>689300</v>
       </c>
       <c r="H49" s="3">
-        <v>880500</v>
+        <v>955400</v>
       </c>
       <c r="I49" s="3">
-        <v>1103200</v>
+        <v>1166000</v>
       </c>
       <c r="J49" s="3">
-        <v>869400</v>
+        <v>911500</v>
       </c>
       <c r="K49" s="3">
         <v>885500</v>
@@ -2489,22 +2489,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>33000</v>
+        <v>20900</v>
       </c>
       <c r="E52" s="3">
-        <v>32300</v>
+        <v>14800</v>
       </c>
       <c r="F52" s="3">
-        <v>52400</v>
+        <v>14900</v>
       </c>
       <c r="G52" s="3">
-        <v>59500</v>
+        <v>28300</v>
       </c>
       <c r="H52" s="3">
-        <v>51000</v>
+        <v>54500</v>
       </c>
       <c r="I52" s="3">
-        <v>40300</v>
+        <v>21100</v>
       </c>
       <c r="J52" s="3">
         <v>12600</v>
@@ -2706,26 +2706,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="G58" s="3">
-        <v>26600</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>33900</v>
+      </c>
+      <c r="H58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>626000</v>
+        <v>410000</v>
       </c>
       <c r="E59" s="3">
-        <v>376300</v>
+        <v>205500</v>
       </c>
       <c r="F59" s="3">
-        <v>349400</v>
+        <v>183200</v>
       </c>
       <c r="G59" s="3">
-        <v>344800</v>
+        <v>217000</v>
       </c>
       <c r="H59" s="3">
-        <v>155300</v>
+        <v>81600</v>
       </c>
       <c r="I59" s="3">
-        <v>122600</v>
+        <v>48700</v>
       </c>
       <c r="J59" s="3">
-        <v>89800</v>
+        <v>24800</v>
       </c>
       <c r="K59" s="3">
         <v>88000</v>
@@ -2842,19 +2842,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>597000</v>
+        <v>635100</v>
       </c>
       <c r="E61" s="3">
-        <v>413000</v>
+        <v>469000</v>
       </c>
       <c r="F61" s="3">
-        <v>215700</v>
+        <v>273400</v>
       </c>
       <c r="G61" s="3">
-        <v>263300</v>
+        <v>325900</v>
       </c>
       <c r="H61" s="3">
-        <v>293700</v>
+        <v>362500</v>
       </c>
       <c r="I61" s="3">
         <v>221000</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>162900</v>
+        <v>110400</v>
       </c>
       <c r="E62" s="3">
-        <v>111400</v>
+        <v>48200</v>
       </c>
       <c r="F62" s="3">
-        <v>64700</v>
+        <v>1100</v>
       </c>
       <c r="G62" s="3">
-        <v>85500</v>
+        <v>18700</v>
       </c>
       <c r="H62" s="3">
-        <v>82500</v>
+        <v>10400</v>
       </c>
       <c r="I62" s="3">
-        <v>42500</v>
+        <v>15600</v>
       </c>
       <c r="J62" s="3">
-        <v>12300</v>
+        <v>9400</v>
       </c>
       <c r="K62" s="3">
         <v>35500</v>
@@ -3079,13 +3079,13 @@
         <v>752100</v>
       </c>
       <c r="H66" s="3">
-        <v>575700</v>
+        <v>569000</v>
       </c>
       <c r="I66" s="3">
-        <v>578500</v>
+        <v>532900</v>
       </c>
       <c r="J66" s="3">
-        <v>301800</v>
+        <v>266400</v>
       </c>
       <c r="K66" s="3">
         <v>497300</v>
@@ -3631,7 +3631,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-142300</v>
+        <v>-113000</v>
       </c>
       <c r="E81" s="3">
         <v>-19200</v>
@@ -3640,7 +3640,7 @@
         <v>-37600</v>
       </c>
       <c r="G81" s="3">
-        <v>-330600</v>
+        <v>-334200</v>
       </c>
       <c r="H81" s="3">
         <v>-302000</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>123400</v>
+        <v>5700</v>
       </c>
       <c r="E83" s="3">
-        <v>67200</v>
+        <v>5000</v>
       </c>
       <c r="F83" s="3">
-        <v>60000</v>
+        <v>4100</v>
       </c>
       <c r="G83" s="3">
-        <v>61500</v>
+        <v>4300</v>
       </c>
       <c r="H83" s="3">
-        <v>60900</v>
+        <v>5100</v>
       </c>
       <c r="I83" s="3">
-        <v>44500</v>
+        <v>4900</v>
       </c>
       <c r="J83" s="3">
-        <v>32400</v>
+        <v>4700</v>
       </c>
       <c r="K83" s="3">
         <v>17200</v>
@@ -4035,16 +4035,16 @@
         <v>-47500</v>
       </c>
       <c r="F91" s="3">
-        <v>-25000</v>
+        <v>-27500</v>
       </c>
       <c r="G91" s="3">
-        <v>-31800</v>
+        <v>-32100</v>
       </c>
       <c r="H91" s="3">
-        <v>-35500</v>
+        <v>-44100</v>
       </c>
       <c r="I91" s="3">
-        <v>-39600</v>
+        <v>-169800</v>
       </c>
       <c r="J91" s="3">
         <v>-27800</v>

--- a/AAII_Financials/Yearly/EVH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EVH_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>EVH</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2554700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1963900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1352000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>908000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>924600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>687100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>627100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>435000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>254200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>96900</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>25700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2187400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1503400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1035400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>657600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>696600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>513000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>398700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>269400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>155200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>57400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>72400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>30000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>367400</v>
+      </c>
+      <c r="E10" s="3">
         <v>460500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>316600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>250400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>228100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>174100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>228300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>165600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>99000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>39500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-72400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-4300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-2900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,35 +887,36 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E12" s="3">
         <v>26700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>27000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>38500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22100</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,99 +980,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E14" s="3">
         <v>123000</v>
       </c>
-      <c r="E14" s="3">
-        <v>11600</v>
-      </c>
       <c r="F14" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>284000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>214300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>160600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-414100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-46200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>118400</v>
+      </c>
+      <c r="E15" s="3">
         <v>123400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>67200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>60000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>60800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>60300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>44500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>32400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>1200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>700</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2552400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1933100</v>
       </c>
-      <c r="E17" s="3">
-        <v>1347000</v>
-      </c>
       <c r="F17" s="3">
+        <v>1371900</v>
+      </c>
+      <c r="G17" s="3">
         <v>925400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>955500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>781700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>674200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>496900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>491600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-274300</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
       <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
         <v>600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>30800</v>
       </c>
-      <c r="E18" s="3">
-        <v>5000</v>
-      </c>
       <c r="F18" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-17400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-30800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-94600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-47200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-61900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-237400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>371200</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
       <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>25100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19600</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,125 +1212,132 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>61200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>41300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-13000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>10000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-27900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-25200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E21" s="3">
         <v>93000</v>
       </c>
-      <c r="E21" s="3">
-        <v>30900</v>
-      </c>
       <c r="F21" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G21" s="3">
         <v>55700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>39900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-44200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-31200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-220300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>350500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-25200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>21200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-18900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E22" s="3">
         <v>54200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>28300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3600</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,99 +1353,108 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-202400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-62100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-29800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-330500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-330000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-54200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-76400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-237500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>343300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-89400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-43400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-22800</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-6600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-10800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>23500</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-113000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-30300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-328200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-307200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-54200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-69800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-226800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>319800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19300</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-93500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-142300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-37600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-334300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-302000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-52700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-60700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-159700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>330300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19300</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1594,25 +1654,25 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-500</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-7300</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-6100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>1600</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
@@ -1626,12 +1686,15 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-61200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-41300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>13000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-10000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>27900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>25200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-113000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-37600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-334200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-302000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-52700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-60700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-159700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>330300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19300</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-113000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-37600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-334200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-302000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-52700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-60700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-159700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>330300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19300</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,53 +2073,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E41" s="3">
         <v>192800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>188200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>266300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>319000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>101000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>228300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>238400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>134600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>145700</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
         <v>67900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5300</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2051,80 +2140,86 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>1800</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>44300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9400</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>414700</v>
+      </c>
+      <c r="E43" s="3">
         <v>446700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>254700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>130600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>124400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>77400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>82300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>68900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>40600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2149,8 +2244,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2167,9 +2262,12 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2182,219 +2280,234 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>33900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>45400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>607100</v>
+      </c>
+      <c r="E46" s="3">
         <v>683700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>478100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>524000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>547600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>228800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>488000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>378200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>265000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>184500</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3">
         <v>80300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7800</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E47" s="3">
         <v>4900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>139400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>37200</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2400</v>
       </c>
       <c r="O47" s="3">
         <v>2400</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E48" s="3">
         <v>19300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>63200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>60400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>68700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>82400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3800</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1886200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1939500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1239300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>777300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>689300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>955400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1166000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>911500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>885500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>772100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2200</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>20900</v>
+        <v>17100</v>
       </c>
       <c r="E52" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F52" s="3">
         <v>14800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>28300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>54500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1600</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>3500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2544400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2680300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1817300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1419500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1371700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1498000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1722300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1312700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1199800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1015500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>102000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16300</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,79 +2785,83 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E57" s="3">
         <v>48200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>57200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>96100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>37500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>146800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>42900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16700</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>198200</v>
+      </c>
+      <c r="E58" s="3">
         <v>9700</v>
-      </c>
-      <c r="E58" s="3">
-        <v>7100</v>
       </c>
       <c r="F58" s="3">
         <v>7100</v>
       </c>
       <c r="G58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H58" s="3">
         <v>33900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6300</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2736,8 +2869,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2745,129 +2878,138 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>321200</v>
+      </c>
+      <c r="E59" s="3">
         <v>410000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>205500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>183200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>217000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>81600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>48700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>88000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8800</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>715500</v>
+      </c>
+      <c r="E60" s="3">
         <v>674200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>433400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>445500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>403300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>192800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>269400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>132700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>131900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>59500</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3">
         <v>29300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>515500</v>
+      </c>
+      <c r="E61" s="3">
         <v>635100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>469000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>273400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>325900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>362500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>221000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>121400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>120300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2880,54 +3022,60 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>111100</v>
+      </c>
+      <c r="E62" s="3">
         <v>110400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>35500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1353000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1434200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>957900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>725800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>752100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>569000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>532900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>266400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>497300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>366200</v>
       </c>
-      <c r="M66" s="3">
-        <v>0</v>
-      </c>
       <c r="N66" s="3">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3">
         <v>32700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,18 +3378,21 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>190200</v>
+      </c>
+      <c r="E70" s="3">
         <v>178400</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
@@ -3248,20 +3415,23 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>40900</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>69300</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-780800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-719200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-606200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-626800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-589200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-252000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>86000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>146600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>306700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-25800</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
       <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3">
         <v>-20600</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1001300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1067700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>859400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>693600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>619600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>922400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1143800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1010900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>702500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>649300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-3700</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
       <c r="O76" s="3">
+        <v>0</v>
+      </c>
+      <c r="P76" s="3">
         <v>5200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-113000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-37600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-334200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-302000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-52700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-60700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-159700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>330300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19300</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E83" s="3">
         <v>5700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7200</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>1200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E89" s="3">
         <v>142600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-42600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-20700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-35500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-18500</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>-13600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-47500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-32100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-44100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-169800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6500</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-10400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-62900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-415500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-259100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>261100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-181600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-160400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-96700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-43700</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-25900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,77 +4643,83 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>281300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>131500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-29500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-35500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>274000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>165600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>150200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>214200</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>34300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4500</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -4488,55 +4736,61 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-45000</v>
+      </c>
+      <c r="E102" s="3">
         <v>8300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-139800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>233100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-259800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>93000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>125300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>152000</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-5300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/EVH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EVH_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>EVH</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1876200</v>
+      </c>
+      <c r="E8" s="3">
         <v>2554700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1963900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1352000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>908000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>924600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>687100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>627100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>435000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>254200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>96900</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>25700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8300</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1476300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2187400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1503400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1035400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>657600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>696600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>513000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>398700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>269400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>155200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>57400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>72400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>30000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11300</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>399900</v>
+      </c>
+      <c r="E10" s="3">
         <v>367400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>460500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>316600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>250400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>228100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>174100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>228300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>165600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>99000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>39500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-72400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-4300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,38 +900,39 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E12" s="3">
         <v>25600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>38500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>30600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22100</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,105 +999,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>42800</v>
+        <v>424200</v>
       </c>
       <c r="E14" s="3">
-        <v>123000</v>
+        <v>64400</v>
       </c>
       <c r="F14" s="3">
+        <v>106400</v>
+      </c>
+      <c r="G14" s="3">
         <v>-13300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>284000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>214300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>160600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-414100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-46200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>118400</v>
+        <v>115900</v>
       </c>
       <c r="E15" s="3">
+        <v>96800</v>
+      </c>
+      <c r="F15" s="3">
         <v>123400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>67200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>60000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>60800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>60300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>44500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7200</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
         <v>1200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>700</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2552400</v>
+        <v>1880700</v>
       </c>
       <c r="E17" s="3">
-        <v>1933100</v>
+        <v>2530800</v>
       </c>
       <c r="F17" s="3">
+        <v>1949700</v>
+      </c>
+      <c r="G17" s="3">
         <v>1371900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>925400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>955500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>781700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>674200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>496900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>491600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-274300</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
       <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2300</v>
+        <v>-4400</v>
       </c>
       <c r="E18" s="3">
-        <v>30800</v>
+        <v>23900</v>
       </c>
       <c r="F18" s="3">
+        <v>14200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-19900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-17400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-94600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-47200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-61900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-237400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>371200</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
         <v>25100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,134 +1245,141 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E20" s="3">
         <v>3400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>61200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>41300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-13000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-27900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-25200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E21" s="3">
         <v>117300</v>
       </c>
-      <c r="E21" s="3">
-        <v>93000</v>
-      </c>
       <c r="F21" s="3">
+        <v>76400</v>
+      </c>
+      <c r="G21" s="3">
         <v>6000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>55700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>39900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-44200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-31200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-220300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>350500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-25200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>21200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E22" s="3">
         <v>24700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>54200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>28300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3600</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,105 +1395,114 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-534600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-63000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-202400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-62100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-330500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-330000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-54200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-76400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-237500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>343300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>20000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-89400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-43400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-22800</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-6600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23500</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-534500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-61600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-113000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-30300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-328200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-307200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-54200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-69800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-226800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>319800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>20000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-579400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-93500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-142300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-37600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-334300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-302000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-52700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-60700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-159700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>330300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1657,25 +1717,25 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-500</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-7300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-6100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1600</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
@@ -1689,12 +1749,15 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-52700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-61200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-41300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>13000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>27900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>25200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-534500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-61600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-113000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-37600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-334200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-302000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-52700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-60700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-159700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>330300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-534500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-61600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-113000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-37600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-334200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-302000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-52700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-60700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-159700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>330300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,56 +2159,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>151900</v>
+      </c>
+      <c r="E41" s="3">
         <v>104200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>192800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>188200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>266300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>319000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>101000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>228300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>238400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>134600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>145700</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
       <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
         <v>67900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,83 +2232,89 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>1800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>44300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9400</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>309900</v>
+      </c>
+      <c r="E43" s="3">
         <v>414700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>446700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>254700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>130600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>124400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>77400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>82300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>68900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>40600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2247,8 +2342,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2265,9 +2360,12 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2283,231 +2381,246 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>33900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>45400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>506400</v>
+      </c>
+      <c r="E46" s="3">
         <v>607100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>683700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>478100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>524000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>547600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>228800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>488000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>378200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>265000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>184500</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
       <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3">
         <v>80300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E47" s="3">
         <v>8600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>139400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>16300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>37200</v>
-      </c>
-      <c r="O47" s="3">
-        <v>2400</v>
       </c>
       <c r="P47" s="3">
         <v>2400</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E48" s="3">
         <v>10600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>63200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>60400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>68700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>82400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1357200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1886200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1939500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1239300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>777300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>689300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>955400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1166000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>911500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>885500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>772100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2200</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E52" s="3">
         <v>17100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>54500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1600</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>3500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1899200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2544400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2680300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1817300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1419500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1371700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1498000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1722300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1312700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1199800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1015500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>102000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,85 +2915,89 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E57" s="3">
         <v>96000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>48200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>57200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>96100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>37500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>146800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>42900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>43900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16700</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
         <v>2000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2200</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E58" s="3">
         <v>198200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>7100</v>
       </c>
       <c r="G58" s="3">
         <v>7100</v>
       </c>
       <c r="H58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I58" s="3">
         <v>33900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6300</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2872,8 +3005,8 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2881,138 +3014,147 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>193400</v>
+      </c>
+      <c r="E59" s="3">
         <v>321200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>410000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>205500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>183200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>217000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>81600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>48700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>88000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>385300</v>
+      </c>
+      <c r="E60" s="3">
         <v>715500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>674200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>433400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>445500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>403300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>192800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>269400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>132700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>131900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>59500</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
       <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3">
         <v>29300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>974400</v>
+      </c>
+      <c r="E61" s="3">
         <v>515500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>635100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>469000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>273400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>325900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>362500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>221000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>121400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>120300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3025,57 +3167,63 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>116800</v>
+      </c>
+      <c r="E62" s="3">
         <v>111100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>110400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>48200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>35500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1484000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1353000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1434200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>957900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>725800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>752100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>569000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>532900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>266400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>497300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>366200</v>
       </c>
-      <c r="N66" s="3">
-        <v>0</v>
-      </c>
       <c r="O66" s="3">
+        <v>0</v>
+      </c>
+      <c r="P66" s="3">
         <v>32700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,21 +3545,24 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
         <v>190200</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>178400</v>
       </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
         <v>0</v>
       </c>
@@ -3418,20 +3585,23 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>40900</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>69300</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1315300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-780800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-719200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-606200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-626800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-589200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-252000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>50000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>86000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>146600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>306700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-25800</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
       <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>415200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1001300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1067700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>859400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>693600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>619600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>922400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1143800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1010900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>702500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>649300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-3700</v>
       </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
       <c r="P76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="3">
         <v>5200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-534500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-61600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-113000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-37600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-334200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-302000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-52700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-60700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-159700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>330300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E83" s="3">
         <v>4700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>17200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7200</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E89" s="3">
         <v>18800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>142600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-42600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-20700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-35500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-18500</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-13600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-33100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-47500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-32100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-44100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-169800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6500</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-10400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-62900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-415500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-259100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>261100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-181600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-160400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-96700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-43700</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-25900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,8 +4687,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,83 +4888,89 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>281300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>131500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-29500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-35500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>274000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>165600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>150200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>214200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>34300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4500</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -4739,58 +4987,64 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-45000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-139800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>233100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-259800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>93000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>125300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>152000</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-5300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
